--- a/Employee_accounts_roles.xlsx
+++ b/Employee_accounts_roles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\justi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A80432-FC75-4079-8949-5DE77C01E4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56F6D05-F82E-4F99-A24B-22CC535C7141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="359">
   <si>
     <t>Employee ID</t>
   </si>
@@ -1091,6 +1091,12 @@
   </si>
   <si>
     <t>Purchasing Staff I</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
@@ -1146,29 +1152,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table12" displayName="Table12" ref="A1:F129" totalsRowShown="0">
-  <autoFilter ref="A1:F129" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Acquired Properties"/>
-      </filters>
-    </filterColumn>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table12" displayName="Table12" ref="A1:G129" totalsRowShown="0">
+  <autoFilter ref="A1:G129" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="5">
       <filters>
-        <filter val="R&amp;F"/>
+        <filter val="Office of the President"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F129">
-    <sortCondition ref="E1:E129"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:F18">
+    <sortCondition ref="D1:D129"/>
   </sortState>
-  <tableColumns count="6">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Employee ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First Name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last Name"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Position"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Department"/>
-    <tableColumn id="6" xr3:uid="{9739FA01-8447-4721-8D1A-A220C9BEF9FC}" name="Rank"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Password"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="First Name"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Last Name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Position"/>
+    <tableColumn id="6" xr3:uid="{9739FA01-8447-4721-8D1A-A220C9BEF9FC}" name="Department"/>
+    <tableColumn id="7" xr3:uid="{02898C99-3970-4E09-BC01-29ED21D9C7DC}" name="Rank"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1460,2598 +1462,2984 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
       <c r="B7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>35</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
       <c r="B9" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>358</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B14" t="s">
+        <v>358</v>
+      </c>
+      <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D14" t="s">
         <v>43</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E14" t="s">
         <v>44</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
       <c r="B15" t="s">
+        <v>358</v>
+      </c>
+      <c r="C15" t="s">
         <v>61</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>62</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>63</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>10</v>
       </c>
-      <c r="F15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>358</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" t="s">
+        <v>358</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>64</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B18" t="s">
+        <v>358</v>
+      </c>
+      <c r="C18" t="s">
         <v>65</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D18" t="s">
         <v>66</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E18" t="s">
         <v>67</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F18" t="s">
         <v>10</v>
       </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
       <c r="B19" t="s">
+        <v>358</v>
+      </c>
+      <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>76</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>77</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>78</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>79</v>
       </c>
       <c r="B20" t="s">
+        <v>358</v>
+      </c>
+      <c r="C20" t="s">
         <v>80</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>69</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>81</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>78</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>82</v>
       </c>
       <c r="B21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C21" t="s">
         <v>83</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>84</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>85</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>78</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" t="s">
         <v>87</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>88</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>89</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>78</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>90</v>
       </c>
       <c r="B23" t="s">
+        <v>358</v>
+      </c>
+      <c r="C23" t="s">
         <v>91</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>62</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>92</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>78</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>93</v>
       </c>
       <c r="B24" t="s">
+        <v>358</v>
+      </c>
+      <c r="C24" t="s">
         <v>13</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>94</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>95</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>78</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>96</v>
       </c>
       <c r="B25" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>97</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>98</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>78</v>
       </c>
-      <c r="F25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>99</v>
       </c>
       <c r="B26" t="s">
+        <v>358</v>
+      </c>
+      <c r="C26" t="s">
         <v>100</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>66</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>101</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>78</v>
       </c>
-      <c r="F26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>102</v>
       </c>
       <c r="B27" t="s">
+        <v>358</v>
+      </c>
+      <c r="C27" t="s">
         <v>53</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>8</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>103</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>78</v>
       </c>
-      <c r="F27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>104</v>
       </c>
       <c r="B28" t="s">
+        <v>358</v>
+      </c>
+      <c r="C28" t="s">
         <v>105</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>69</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>106</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>78</v>
       </c>
-      <c r="F28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>107</v>
       </c>
       <c r="B29" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29" t="s">
         <v>108</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>43</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>109</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>78</v>
       </c>
-      <c r="F29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>110</v>
       </c>
       <c r="B30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C30" t="s">
         <v>111</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>27</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>112</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>78</v>
       </c>
-      <c r="F30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>113</v>
       </c>
       <c r="B31" t="s">
+        <v>358</v>
+      </c>
+      <c r="C31" t="s">
         <v>114</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>115</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>116</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>117</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>118</v>
       </c>
       <c r="B32" t="s">
+        <v>358</v>
+      </c>
+      <c r="C32" t="s">
         <v>69</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>14</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>119</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>117</v>
       </c>
-      <c r="F32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33" t="s">
+        <v>358</v>
+      </c>
+      <c r="C33" t="s">
         <v>121</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>122</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>123</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>117</v>
       </c>
-      <c r="F33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>124</v>
       </c>
       <c r="B34" t="s">
+        <v>358</v>
+      </c>
+      <c r="C34" t="s">
         <v>7</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>14</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>125</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>117</v>
       </c>
-      <c r="F34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>126</v>
       </c>
       <c r="B35" t="s">
+        <v>358</v>
+      </c>
+      <c r="C35" t="s">
         <v>127</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>54</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>128</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>129</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>130</v>
       </c>
       <c r="B36" t="s">
+        <v>358</v>
+      </c>
+      <c r="C36" t="s">
         <v>121</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>35</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>131</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>129</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>132</v>
       </c>
       <c r="B37" t="s">
+        <v>358</v>
+      </c>
+      <c r="C37" t="s">
         <v>22</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>133</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>134</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>129</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>135</v>
       </c>
       <c r="B38" t="s">
+        <v>358</v>
+      </c>
+      <c r="C38" t="s">
         <v>83</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>97</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>136</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>129</v>
       </c>
-      <c r="F38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>137</v>
       </c>
       <c r="B39" t="s">
+        <v>358</v>
+      </c>
+      <c r="C39" t="s">
         <v>114</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>70</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>138</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>129</v>
       </c>
-      <c r="F39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>139</v>
       </c>
       <c r="B40" t="s">
+        <v>358</v>
+      </c>
+      <c r="C40" t="s">
         <v>140</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>8</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>141</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>129</v>
       </c>
-      <c r="F40" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>142</v>
       </c>
       <c r="B41" t="s">
+        <v>358</v>
+      </c>
+      <c r="C41" t="s">
         <v>143</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>144</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>145</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>146</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>147</v>
       </c>
       <c r="B42" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42" t="s">
         <v>140</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>58</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>148</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>146</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>149</v>
       </c>
       <c r="B43" t="s">
+        <v>358</v>
+      </c>
+      <c r="C43" t="s">
         <v>83</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>150</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>146</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>151</v>
       </c>
       <c r="B44" t="s">
+        <v>358</v>
+      </c>
+      <c r="C44" t="s">
         <v>152</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>153</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>154</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>146</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>155</v>
       </c>
       <c r="B45" t="s">
+        <v>358</v>
+      </c>
+      <c r="C45" t="s">
         <v>7</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>88</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>156</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>146</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>157</v>
       </c>
       <c r="B46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C46" t="s">
         <v>158</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>35</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>159</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>146</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>160</v>
       </c>
       <c r="B47" t="s">
+        <v>358</v>
+      </c>
+      <c r="C47" t="s">
         <v>161</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>66</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>162</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>146</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>163</v>
       </c>
       <c r="B48" t="s">
+        <v>358</v>
+      </c>
+      <c r="C48" t="s">
         <v>111</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>70</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>164</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>146</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>165</v>
       </c>
       <c r="B49" t="s">
+        <v>358</v>
+      </c>
+      <c r="C49" t="s">
         <v>87</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>39</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>166</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>146</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>167</v>
       </c>
       <c r="B50" t="s">
+        <v>358</v>
+      </c>
+      <c r="C50" t="s">
         <v>53</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>39</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>168</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>146</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>169</v>
       </c>
       <c r="B51" t="s">
+        <v>358</v>
+      </c>
+      <c r="C51" t="s">
         <v>170</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>97</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>171</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>146</v>
       </c>
-      <c r="F51" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>172</v>
       </c>
       <c r="B52" t="s">
+        <v>358</v>
+      </c>
+      <c r="C52" t="s">
         <v>173</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>8</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>174</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>146</v>
       </c>
-      <c r="F52" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>175</v>
       </c>
       <c r="B53" t="s">
+        <v>358</v>
+      </c>
+      <c r="C53" t="s">
         <v>176</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>177</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>178</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>146</v>
       </c>
-      <c r="F53" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>179</v>
       </c>
       <c r="B54" t="s">
+        <v>358</v>
+      </c>
+      <c r="C54" t="s">
         <v>114</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>58</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>180</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>146</v>
       </c>
-      <c r="F54" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>181</v>
       </c>
       <c r="B55" t="s">
+        <v>358</v>
+      </c>
+      <c r="C55" t="s">
         <v>26</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>133</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>182</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>146</v>
       </c>
-      <c r="F55" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>183</v>
       </c>
       <c r="B56" t="s">
+        <v>358</v>
+      </c>
+      <c r="C56" t="s">
         <v>87</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>54</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>184</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>146</v>
       </c>
-      <c r="F56" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>185</v>
       </c>
       <c r="B57" t="s">
+        <v>358</v>
+      </c>
+      <c r="C57" t="s">
         <v>87</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>133</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>186</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>146</v>
       </c>
-      <c r="F57" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>187</v>
       </c>
       <c r="B58" t="s">
+        <v>358</v>
+      </c>
+      <c r="C58" t="s">
         <v>83</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>122</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>188</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>146</v>
       </c>
-      <c r="F58" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>113</v>
       </c>
       <c r="B59" t="s">
+        <v>358</v>
+      </c>
+      <c r="C59" t="s">
         <v>114</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>115</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>116</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>189</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>118</v>
       </c>
       <c r="B60" t="s">
+        <v>358</v>
+      </c>
+      <c r="C60" t="s">
         <v>69</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>14</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>119</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>189</v>
       </c>
-      <c r="F60" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>120</v>
       </c>
       <c r="B61" t="s">
+        <v>358</v>
+      </c>
+      <c r="C61" t="s">
         <v>121</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>122</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>123</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>189</v>
       </c>
-      <c r="F61" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>124</v>
       </c>
       <c r="B62" t="s">
+        <v>358</v>
+      </c>
+      <c r="C62" t="s">
         <v>7</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>14</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>125</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>189</v>
       </c>
-      <c r="F62" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>190</v>
       </c>
       <c r="B63" t="s">
+        <v>358</v>
+      </c>
+      <c r="C63" t="s">
         <v>61</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>191</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>192</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>193</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>194</v>
       </c>
       <c r="B64" t="s">
+        <v>358</v>
+      </c>
+      <c r="C64" t="s">
         <v>195</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>27</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>196</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>193</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>197</v>
       </c>
       <c r="B65" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" t="s">
         <v>198</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>97</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>199</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>193</v>
       </c>
-      <c r="F65" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G65" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>200</v>
       </c>
       <c r="B66" t="s">
+        <v>358</v>
+      </c>
+      <c r="C66" t="s">
         <v>201</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>97</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>202</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>193</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>203</v>
       </c>
       <c r="B67" t="s">
+        <v>358</v>
+      </c>
+      <c r="C67" t="s">
         <v>105</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>144</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>204</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>193</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>205</v>
       </c>
       <c r="B68" t="s">
+        <v>358</v>
+      </c>
+      <c r="C68" t="s">
         <v>105</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>133</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>206</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>193</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>207</v>
       </c>
       <c r="B69" t="s">
+        <v>358</v>
+      </c>
+      <c r="C69" t="s">
         <v>208</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>209</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>210</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>193</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>211</v>
       </c>
       <c r="B70" t="s">
+        <v>358</v>
+      </c>
+      <c r="C70" t="s">
         <v>13</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>84</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>212</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>193</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>213</v>
       </c>
       <c r="B71" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71" t="s">
         <v>214</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>70</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>215</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>193</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>216</v>
       </c>
       <c r="B72" t="s">
+        <v>358</v>
+      </c>
+      <c r="C72" t="s">
         <v>217</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>8</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>218</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>193</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>219</v>
       </c>
       <c r="B73" t="s">
+        <v>358</v>
+      </c>
+      <c r="C73" t="s">
         <v>50</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>220</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>221</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>193</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>222</v>
       </c>
       <c r="B74" t="s">
+        <v>358</v>
+      </c>
+      <c r="C74" t="s">
         <v>195</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>58</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>223</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>193</v>
       </c>
-      <c r="F74" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G74" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>224</v>
       </c>
       <c r="B75" t="s">
+        <v>358</v>
+      </c>
+      <c r="C75" t="s">
         <v>225</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>70</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>226</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>193</v>
       </c>
-      <c r="F75" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G75" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>227</v>
       </c>
       <c r="B76" t="s">
+        <v>358</v>
+      </c>
+      <c r="C76" t="s">
         <v>140</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>62</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>228</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>193</v>
       </c>
-      <c r="F76" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G76" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>229</v>
       </c>
       <c r="B77" t="s">
+        <v>358</v>
+      </c>
+      <c r="C77" t="s">
         <v>42</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>35</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>230</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>193</v>
       </c>
-      <c r="F77" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G77" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>231</v>
       </c>
       <c r="B78" t="s">
+        <v>358</v>
+      </c>
+      <c r="C78" t="s">
         <v>100</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>177</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>232</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>193</v>
       </c>
-      <c r="F78" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G78" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>233</v>
       </c>
       <c r="B79" t="s">
+        <v>358</v>
+      </c>
+      <c r="C79" t="s">
         <v>234</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>76</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>235</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>236</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>237</v>
       </c>
       <c r="B80" t="s">
+        <v>358</v>
+      </c>
+      <c r="C80" t="s">
         <v>105</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>209</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>238</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>236</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>239</v>
       </c>
       <c r="B81" t="s">
+        <v>358</v>
+      </c>
+      <c r="C81" t="s">
         <v>240</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>76</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>241</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>236</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>242</v>
       </c>
       <c r="B82" t="s">
+        <v>358</v>
+      </c>
+      <c r="C82" t="s">
         <v>176</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>84</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>243</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>236</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>244</v>
       </c>
       <c r="B83" t="s">
+        <v>358</v>
+      </c>
+      <c r="C83" t="s">
         <v>245</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>27</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>246</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>236</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>247</v>
       </c>
       <c r="B84" t="s">
+        <v>358</v>
+      </c>
+      <c r="C84" t="s">
         <v>217</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>54</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>248</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>236</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>249</v>
       </c>
       <c r="B85" t="s">
+        <v>358</v>
+      </c>
+      <c r="C85" t="s">
         <v>152</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>69</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>250</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>236</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>251</v>
       </c>
       <c r="B86" t="s">
+        <v>358</v>
+      </c>
+      <c r="C86" t="s">
         <v>143</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>88</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>252</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>236</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>253</v>
       </c>
       <c r="B87" t="s">
+        <v>358</v>
+      </c>
+      <c r="C87" t="s">
         <v>234</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>220</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>254</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>236</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>255</v>
       </c>
       <c r="B88" t="s">
+        <v>358</v>
+      </c>
+      <c r="C88" t="s">
         <v>208</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>122</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>256</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>236</v>
       </c>
-      <c r="F88" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G88" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>257</v>
       </c>
       <c r="B89" t="s">
+        <v>358</v>
+      </c>
+      <c r="C89" t="s">
         <v>258</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>94</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>259</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>236</v>
       </c>
-      <c r="F89" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G89" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>260</v>
       </c>
       <c r="B90" t="s">
+        <v>358</v>
+      </c>
+      <c r="C90" t="s">
         <v>100</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>122</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>261</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>236</v>
       </c>
-      <c r="F90" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G90" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>262</v>
       </c>
       <c r="B91" t="s">
+        <v>358</v>
+      </c>
+      <c r="C91" t="s">
         <v>263</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>220</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>264</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>236</v>
       </c>
-      <c r="F91" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G91" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>265</v>
       </c>
       <c r="B92" t="s">
+        <v>358</v>
+      </c>
+      <c r="C92" t="s">
         <v>140</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>266</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>267</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>236</v>
       </c>
-      <c r="F92" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G92" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>268</v>
       </c>
       <c r="B93" t="s">
+        <v>358</v>
+      </c>
+      <c r="C93" t="s">
         <v>50</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>177</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>269</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>236</v>
       </c>
-      <c r="F93" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G93" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>270</v>
       </c>
       <c r="B94" t="s">
+        <v>358</v>
+      </c>
+      <c r="C94" t="s">
         <v>271</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>94</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>272</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>236</v>
       </c>
-      <c r="F94" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G94" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>273</v>
       </c>
       <c r="B95" t="s">
+        <v>358</v>
+      </c>
+      <c r="C95" t="s">
         <v>274</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>66</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>275</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>236</v>
       </c>
-      <c r="F95" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G95" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>276</v>
       </c>
       <c r="B96" t="s">
+        <v>358</v>
+      </c>
+      <c r="C96" t="s">
         <v>277</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>23</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>278</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>236</v>
       </c>
-      <c r="F96" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G96" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>279</v>
       </c>
       <c r="B97" t="s">
+        <v>358</v>
+      </c>
+      <c r="C97" t="s">
         <v>61</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>19</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>280</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>236</v>
       </c>
-      <c r="F97" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G97" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>281</v>
       </c>
       <c r="B98" t="s">
+        <v>358</v>
+      </c>
+      <c r="C98" t="s">
         <v>75</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>94</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>282</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>283</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>284</v>
       </c>
       <c r="B99" t="s">
+        <v>358</v>
+      </c>
+      <c r="C99" t="s">
         <v>285</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>14</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>286</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>283</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>287</v>
       </c>
       <c r="B100" t="s">
+        <v>358</v>
+      </c>
+      <c r="C100" t="s">
         <v>50</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>144</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>288</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>283</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>289</v>
       </c>
       <c r="B101" t="s">
+        <v>358</v>
+      </c>
+      <c r="C101" t="s">
         <v>91</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>69</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>290</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>283</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>291</v>
       </c>
       <c r="B102" t="s">
+        <v>358</v>
+      </c>
+      <c r="C102" t="s">
         <v>263</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>153</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>292</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>283</v>
       </c>
-      <c r="F102" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G102" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>293</v>
       </c>
       <c r="B103" t="s">
+        <v>358</v>
+      </c>
+      <c r="C103" t="s">
         <v>108</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>14</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>294</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>283</v>
       </c>
-      <c r="F103" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G103" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>295</v>
       </c>
       <c r="B104" t="s">
+        <v>358</v>
+      </c>
+      <c r="C104" t="s">
         <v>201</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>296</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>297</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>283</v>
       </c>
-      <c r="F104" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G104" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>298</v>
       </c>
       <c r="B105" t="s">
+        <v>358</v>
+      </c>
+      <c r="C105" t="s">
         <v>214</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>266</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>299</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>300</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>301</v>
       </c>
       <c r="B106" t="s">
+        <v>358</v>
+      </c>
+      <c r="C106" t="s">
         <v>302</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>133</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>303</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>300</v>
       </c>
-      <c r="F106" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G106" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>304</v>
       </c>
       <c r="B107" t="s">
+        <v>358</v>
+      </c>
+      <c r="C107" t="s">
         <v>305</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>122</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>306</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>300</v>
       </c>
-      <c r="F107" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G107" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>307</v>
       </c>
       <c r="B108" t="s">
+        <v>358</v>
+      </c>
+      <c r="C108" t="s">
         <v>170</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>266</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>308</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>300</v>
       </c>
-      <c r="F108" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G108" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>309</v>
       </c>
       <c r="B109" t="s">
+        <v>358</v>
+      </c>
+      <c r="C109" t="s">
         <v>258</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>144</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>310</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>311</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>312</v>
       </c>
       <c r="B110" t="s">
+        <v>358</v>
+      </c>
+      <c r="C110" t="s">
         <v>263</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>266</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>313</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>311</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>314</v>
       </c>
       <c r="B111" t="s">
+        <v>358</v>
+      </c>
+      <c r="C111" t="s">
         <v>315</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>97</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>316</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>311</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>317</v>
       </c>
       <c r="B112" t="s">
+        <v>358</v>
+      </c>
+      <c r="C112" t="s">
         <v>271</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>266</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>318</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>311</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>319</v>
       </c>
       <c r="B113" t="s">
+        <v>358</v>
+      </c>
+      <c r="C113" t="s">
         <v>91</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>54</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>320</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>311</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>321</v>
       </c>
       <c r="B114" t="s">
+        <v>358</v>
+      </c>
+      <c r="C114" t="s">
         <v>87</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>94</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>322</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>311</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>323</v>
       </c>
       <c r="B115" t="s">
+        <v>358</v>
+      </c>
+      <c r="C115" t="s">
         <v>324</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>54</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>325</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>311</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>326</v>
       </c>
       <c r="B116" t="s">
+        <v>358</v>
+      </c>
+      <c r="C116" t="s">
         <v>61</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>153</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>327</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>311</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>328</v>
       </c>
       <c r="B117" t="s">
+        <v>358</v>
+      </c>
+      <c r="C117" t="s">
         <v>69</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>8</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>329</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>311</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>330</v>
       </c>
       <c r="B118" t="s">
+        <v>358</v>
+      </c>
+      <c r="C118" t="s">
         <v>143</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>133</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>331</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>311</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>332</v>
       </c>
       <c r="B119" t="s">
+        <v>358</v>
+      </c>
+      <c r="C119" t="s">
         <v>53</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>14</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>333</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>311</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>334</v>
       </c>
       <c r="B120" t="s">
+        <v>358</v>
+      </c>
+      <c r="C120" t="s">
         <v>208</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>39</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>335</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>311</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>336</v>
       </c>
       <c r="B121" t="s">
+        <v>358</v>
+      </c>
+      <c r="C121" t="s">
         <v>53</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>27</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>337</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>311</v>
       </c>
-      <c r="F121" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G121" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>338</v>
       </c>
       <c r="B122" t="s">
+        <v>358</v>
+      </c>
+      <c r="C122" t="s">
         <v>324</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>14</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>339</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>311</v>
       </c>
-      <c r="F122" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G122" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>340</v>
       </c>
       <c r="B123" t="s">
+        <v>358</v>
+      </c>
+      <c r="C123" t="s">
         <v>271</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>177</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>341</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>311</v>
       </c>
-      <c r="F123" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G123" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>342</v>
       </c>
       <c r="B124" t="s">
+        <v>358</v>
+      </c>
+      <c r="C124" t="s">
         <v>277</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>343</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>344</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>311</v>
       </c>
-      <c r="F124" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G124" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>345</v>
       </c>
       <c r="B125" t="s">
+        <v>358</v>
+      </c>
+      <c r="C125" t="s">
         <v>170</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>220</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>346</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>311</v>
       </c>
-      <c r="F125" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G125" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>347</v>
       </c>
       <c r="B126" t="s">
+        <v>358</v>
+      </c>
+      <c r="C126" t="s">
         <v>263</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>54</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
         <v>348</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>311</v>
       </c>
-      <c r="F126" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G126" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>349</v>
       </c>
       <c r="B127" t="s">
+        <v>358</v>
+      </c>
+      <c r="C127" t="s">
         <v>350</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
         <v>23</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>351</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>352</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>353</v>
       </c>
       <c r="B128" t="s">
+        <v>358</v>
+      </c>
+      <c r="C128" t="s">
         <v>285</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>144</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>354</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>352</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>355</v>
       </c>
       <c r="B129" t="s">
+        <v>358</v>
+      </c>
+      <c r="C129" t="s">
         <v>114</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>69</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>356</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>352</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>45</v>
       </c>
     </row>

--- a/Employee_accounts_roles.xlsx
+++ b/Employee_accounts_roles.xlsx
@@ -5,22 +5,37 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\justi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\FINAL_RAQUEL_PAWNSHOP_HRD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56F6D05-F82E-4F99-A24B-22CC535C7141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15E1784-C1D5-46AF-9690-5FD0A01A8A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
+    <sheet name="Department and Positions" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Department and Positions'!$A$1:$B$151</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="388">
   <si>
     <t>Employee ID</t>
   </si>
@@ -1097,16 +1112,111 @@
   </si>
   <si>
     <t>password</t>
+  </si>
+  <si>
+    <t>DEPARTMENT</t>
+  </si>
+  <si>
+    <t>Human resources</t>
+  </si>
+  <si>
+    <t>Positions</t>
+  </si>
+  <si>
+    <t>VP for General Services</t>
+  </si>
+  <si>
+    <t>GS Manager I</t>
+  </si>
+  <si>
+    <t>GS Manager II</t>
+  </si>
+  <si>
+    <t>GS Manager III</t>
+  </si>
+  <si>
+    <t>GS Manager IV</t>
+  </si>
+  <si>
+    <t>GS Supervisor I</t>
+  </si>
+  <si>
+    <t>GS Supervisor II</t>
+  </si>
+  <si>
+    <t>GS Supervisor III</t>
+  </si>
+  <si>
+    <t>GS Supervisor IV</t>
+  </si>
+  <si>
+    <t>Driver I</t>
+  </si>
+  <si>
+    <t>Driver II</t>
+  </si>
+  <si>
+    <t>Driver III</t>
+  </si>
+  <si>
+    <t>Driver IV</t>
+  </si>
+  <si>
+    <t>Driver V</t>
+  </si>
+  <si>
+    <t>Security Monitoring Staff I</t>
+  </si>
+  <si>
+    <t>Security Monitoring Staff II</t>
+  </si>
+  <si>
+    <t>Security Monitoring Staff III</t>
+  </si>
+  <si>
+    <t>Security Monitoring Staff IV</t>
+  </si>
+  <si>
+    <t>Facilities Maintenance Staff I</t>
+  </si>
+  <si>
+    <t>Facilities Maintenance Staff III</t>
+  </si>
+  <si>
+    <t>Warehouse Staff I</t>
+  </si>
+  <si>
+    <t>Messenger I</t>
+  </si>
+  <si>
+    <t>Messenger II</t>
+  </si>
+  <si>
+    <t>Position Count</t>
+  </si>
+  <si>
+    <t>Accounting Manager I</t>
+  </si>
+  <si>
+    <t>Facilities Maintenance Staff II</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1120,7 +1230,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1128,12 +1238,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1153,13 +1295,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table12" displayName="Table12" ref="A1:G129" totalsRowShown="0">
-  <autoFilter ref="A1:G129" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Office of the President"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G129" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:F18">
     <sortCondition ref="D1:D129"/>
   </sortState>
@@ -1499,7 +1635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1522,7 +1658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1545,7 +1681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1568,7 +1704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1591,7 +1727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1614,7 +1750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1637,7 +1773,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1660,7 +1796,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1683,7 +1819,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1706,7 +1842,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1729,7 +1865,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1752,7 +1888,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -1775,7 +1911,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1798,7 +1934,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1821,7 +1957,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1844,7 +1980,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -1867,7 +2003,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1890,7 +2026,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1913,7 +2049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -1936,7 +2072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -1959,7 +2095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -1982,7 +2118,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -2005,7 +2141,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -2028,7 +2164,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -2051,7 +2187,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>99</v>
       </c>
@@ -2074,7 +2210,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>102</v>
       </c>
@@ -2097,7 +2233,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>104</v>
       </c>
@@ -2120,7 +2256,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>107</v>
       </c>
@@ -2143,7 +2279,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -2166,7 +2302,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -2189,7 +2325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -2212,7 +2348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>120</v>
       </c>
@@ -2235,7 +2371,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>124</v>
       </c>
@@ -2258,7 +2394,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>126</v>
       </c>
@@ -2281,7 +2417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>130</v>
       </c>
@@ -2304,7 +2440,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2327,7 +2463,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>135</v>
       </c>
@@ -2350,7 +2486,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -2373,7 +2509,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2396,7 +2532,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>142</v>
       </c>
@@ -2419,7 +2555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>147</v>
       </c>
@@ -2442,7 +2578,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>149</v>
       </c>
@@ -2465,7 +2601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -2488,7 +2624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>155</v>
       </c>
@@ -2511,7 +2647,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>157</v>
       </c>
@@ -2534,7 +2670,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>160</v>
       </c>
@@ -2557,7 +2693,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>163</v>
       </c>
@@ -2580,7 +2716,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>165</v>
       </c>
@@ -2603,7 +2739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>167</v>
       </c>
@@ -2626,7 +2762,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>169</v>
       </c>
@@ -2649,7 +2785,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>172</v>
       </c>
@@ -2672,7 +2808,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>175</v>
       </c>
@@ -2695,7 +2831,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>179</v>
       </c>
@@ -2718,7 +2854,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>181</v>
       </c>
@@ -2741,7 +2877,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>183</v>
       </c>
@@ -2764,7 +2900,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>185</v>
       </c>
@@ -2787,7 +2923,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>187</v>
       </c>
@@ -2810,7 +2946,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>113</v>
       </c>
@@ -2833,7 +2969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -2856,7 +2992,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -2879,7 +3015,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>124</v>
       </c>
@@ -2902,7 +3038,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>190</v>
       </c>
@@ -2925,7 +3061,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>194</v>
       </c>
@@ -2948,7 +3084,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>197</v>
       </c>
@@ -2971,7 +3107,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>200</v>
       </c>
@@ -2994,7 +3130,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>203</v>
       </c>
@@ -3017,7 +3153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>205</v>
       </c>
@@ -3040,7 +3176,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>207</v>
       </c>
@@ -3063,7 +3199,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>211</v>
       </c>
@@ -3086,7 +3222,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>213</v>
       </c>
@@ -3109,7 +3245,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>216</v>
       </c>
@@ -3132,7 +3268,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>219</v>
       </c>
@@ -3155,7 +3291,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>222</v>
       </c>
@@ -3178,7 +3314,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>224</v>
       </c>
@@ -3201,7 +3337,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>227</v>
       </c>
@@ -3224,7 +3360,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>229</v>
       </c>
@@ -3247,7 +3383,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>231</v>
       </c>
@@ -3270,7 +3406,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>233</v>
       </c>
@@ -3293,7 +3429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>237</v>
       </c>
@@ -3316,7 +3452,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>239</v>
       </c>
@@ -3339,7 +3475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>242</v>
       </c>
@@ -3362,7 +3498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>244</v>
       </c>
@@ -3385,7 +3521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>247</v>
       </c>
@@ -3408,7 +3544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>249</v>
       </c>
@@ -3431,7 +3567,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>251</v>
       </c>
@@ -3454,7 +3590,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>253</v>
       </c>
@@ -3477,7 +3613,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>255</v>
       </c>
@@ -3500,7 +3636,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>257</v>
       </c>
@@ -3523,7 +3659,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>260</v>
       </c>
@@ -3546,7 +3682,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>262</v>
       </c>
@@ -3569,7 +3705,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>265</v>
       </c>
@@ -3592,7 +3728,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>268</v>
       </c>
@@ -3615,7 +3751,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>270</v>
       </c>
@@ -3638,7 +3774,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>273</v>
       </c>
@@ -3661,7 +3797,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>276</v>
       </c>
@@ -3684,7 +3820,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>279</v>
       </c>
@@ -3707,7 +3843,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>281</v>
       </c>
@@ -3730,7 +3866,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>284</v>
       </c>
@@ -3753,7 +3889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>287</v>
       </c>
@@ -3776,7 +3912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>289</v>
       </c>
@@ -3799,7 +3935,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>291</v>
       </c>
@@ -3822,7 +3958,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>293</v>
       </c>
@@ -3845,7 +3981,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>295</v>
       </c>
@@ -3960,7 +4096,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>309</v>
       </c>
@@ -3983,7 +4119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>312</v>
       </c>
@@ -4006,7 +4142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>314</v>
       </c>
@@ -4029,7 +4165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>317</v>
       </c>
@@ -4052,7 +4188,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>319</v>
       </c>
@@ -4075,7 +4211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>321</v>
       </c>
@@ -4098,7 +4234,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>323</v>
       </c>
@@ -4121,7 +4257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>326</v>
       </c>
@@ -4144,7 +4280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>328</v>
       </c>
@@ -4167,7 +4303,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>330</v>
       </c>
@@ -4190,7 +4326,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>332</v>
       </c>
@@ -4213,7 +4349,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>334</v>
       </c>
@@ -4236,7 +4372,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>336</v>
       </c>
@@ -4259,7 +4395,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>338</v>
       </c>
@@ -4282,7 +4418,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>340</v>
       </c>
@@ -4305,7 +4441,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>342</v>
       </c>
@@ -4328,7 +4464,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>345</v>
       </c>
@@ -4351,7 +4487,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>347</v>
       </c>
@@ -4374,7 +4510,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>349</v>
       </c>
@@ -4397,7 +4533,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>353</v>
       </c>
@@ -4420,7 +4556,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>355</v>
       </c>
@@ -4449,4 +4585,1236 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6380D992-D95D-4D74-83F3-5AC4F2AEB3BB}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F152"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F1" s="2">
+        <f>SUBTOTAL(103,B2:B149)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>146</v>
+      </c>
+      <c r="B49" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>146</v>
+      </c>
+      <c r="B51" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>146</v>
+      </c>
+      <c r="B52" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>146</v>
+      </c>
+      <c r="B53" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>146</v>
+      </c>
+      <c r="B54" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>146</v>
+      </c>
+      <c r="B55" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>189</v>
+      </c>
+      <c r="B74" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>189</v>
+      </c>
+      <c r="B78" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>189</v>
+      </c>
+      <c r="B79" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B80" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>189</v>
+      </c>
+      <c r="B81" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>189</v>
+      </c>
+      <c r="B82" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>360</v>
+      </c>
+      <c r="B83" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>360</v>
+      </c>
+      <c r="B84" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>360</v>
+      </c>
+      <c r="B85" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>360</v>
+      </c>
+      <c r="B86" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>360</v>
+      </c>
+      <c r="B87" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>360</v>
+      </c>
+      <c r="B88" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>360</v>
+      </c>
+      <c r="B90" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>360</v>
+      </c>
+      <c r="B91" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>360</v>
+      </c>
+      <c r="B92" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>360</v>
+      </c>
+      <c r="B93" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>360</v>
+      </c>
+      <c r="B94" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>360</v>
+      </c>
+      <c r="B95" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>360</v>
+      </c>
+      <c r="B97" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>360</v>
+      </c>
+      <c r="B98" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>236</v>
+      </c>
+      <c r="B99" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>236</v>
+      </c>
+      <c r="B100" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>236</v>
+      </c>
+      <c r="B101" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>236</v>
+      </c>
+      <c r="B102" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>236</v>
+      </c>
+      <c r="B103" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>236</v>
+      </c>
+      <c r="B104" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>236</v>
+      </c>
+      <c r="B105" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>236</v>
+      </c>
+      <c r="B106" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>236</v>
+      </c>
+      <c r="B107" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>236</v>
+      </c>
+      <c r="B108" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>236</v>
+      </c>
+      <c r="B110" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>236</v>
+      </c>
+      <c r="B111" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>236</v>
+      </c>
+      <c r="B112" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>236</v>
+      </c>
+      <c r="B113" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>236</v>
+      </c>
+      <c r="B114" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>236</v>
+      </c>
+      <c r="B115" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>236</v>
+      </c>
+      <c r="B116" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>236</v>
+      </c>
+      <c r="B117" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>283</v>
+      </c>
+      <c r="B118" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>283</v>
+      </c>
+      <c r="B119" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>283</v>
+      </c>
+      <c r="B120" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>283</v>
+      </c>
+      <c r="B121" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>283</v>
+      </c>
+      <c r="B122" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>283</v>
+      </c>
+      <c r="B123" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>283</v>
+      </c>
+      <c r="B124" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>300</v>
+      </c>
+      <c r="B125" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>300</v>
+      </c>
+      <c r="B126" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>300</v>
+      </c>
+      <c r="B127" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>300</v>
+      </c>
+      <c r="B128" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>311</v>
+      </c>
+      <c r="B129" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>311</v>
+      </c>
+      <c r="B130" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>311</v>
+      </c>
+      <c r="B131" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>311</v>
+      </c>
+      <c r="B132" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>311</v>
+      </c>
+      <c r="B133" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>311</v>
+      </c>
+      <c r="B134" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>311</v>
+      </c>
+      <c r="B135" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>311</v>
+      </c>
+      <c r="B136" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>311</v>
+      </c>
+      <c r="B137" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>311</v>
+      </c>
+      <c r="B138" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>311</v>
+      </c>
+      <c r="B139" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>311</v>
+      </c>
+      <c r="B141" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>311</v>
+      </c>
+      <c r="B142" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>311</v>
+      </c>
+      <c r="B143" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>311</v>
+      </c>
+      <c r="B144" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>311</v>
+      </c>
+      <c r="B145" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>352</v>
+      </c>
+      <c r="B147" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>352</v>
+      </c>
+      <c r="B148" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>352</v>
+      </c>
+      <c r="B149" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>189</v>
+      </c>
+      <c r="B152" t="s">
+        <v>384</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B151" xr:uid="{6380D992-D95D-4D74-83F3-5AC4F2AEB3BB}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="General Services"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>